--- a/Libraries/Vehicle/Linkage/Link5_S2LAR/sm_car_data_Linkage_Link5_S2LAR.xlsx
+++ b/Libraries/Vehicle/Linkage/Link5_S2LAR/sm_car_data_Linkage_Link5_S2LAR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Link5_S2LAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE311C3-51FB-4D03-8C2B-4B349D18CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95A90E2-7735-4D40-BAF9-199ECB7F7518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30735" yWindow="0" windowWidth="21600" windowHeight="15585" tabRatio="833" activeTab="1" xr2:uid="{8C42F24B-A2AD-4F52-B2E0-8CD89C371F5D}"/>
+    <workbookView xWindow="17025" yWindow="0" windowWidth="11880" windowHeight="15585" tabRatio="833" firstSheet="2" activeTab="3" xr2:uid="{8C42F24B-A2AD-4F52-B2E0-8CD89C371F5D}"/>
   </bookViews>
   <sheets>
     <sheet name="L5StoLAR_Sedan_HambaLG_f" sheetId="3" r:id="rId1"/>
